--- a/backend/data/financials_by_company/1406.HK.xlsx
+++ b/backend/data/financials_by_company/1406.HK.xlsx
@@ -682,154 +682,160 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45382</v>
+        <v>44651</v>
       </c>
       <c r="B2" t="n">
-        <v>-2239291.870177</v>
+        <v>447344</v>
       </c>
       <c r="C2" t="n">
-        <v>0.074521</v>
+        <v>0.292</v>
       </c>
       <c r="D2" t="n">
-        <v>-12440000</v>
+        <v>40384000</v>
       </c>
       <c r="E2" t="n">
-        <v>-30049000</v>
+        <v>1532000</v>
       </c>
       <c r="F2" t="n">
-        <v>-30049000</v>
+        <v>1532000</v>
       </c>
       <c r="G2" t="n">
-        <v>-75793000</v>
+        <v>13491000</v>
       </c>
       <c r="H2" t="n">
-        <v>37383000</v>
+        <v>22093000</v>
       </c>
       <c r="I2" t="n">
-        <v>37326000</v>
+        <v>38492000</v>
       </c>
       <c r="J2" t="n">
-        <v>-42489000</v>
+        <v>41916000</v>
       </c>
       <c r="K2" t="n">
-        <v>-79872000</v>
+        <v>19823000</v>
       </c>
       <c r="L2" t="n">
-        <v>-80000</v>
+        <v>-6920000</v>
       </c>
       <c r="M2" t="n">
-        <v>2024000</v>
+        <v>777000</v>
       </c>
       <c r="N2" t="n">
-        <v>6224000</v>
+        <v>47000</v>
       </c>
       <c r="O2" t="n">
-        <v>-47983291.870177</v>
+        <v>12406344</v>
       </c>
       <c r="P2" t="n">
-        <v>-75793000</v>
+        <v>13491000</v>
       </c>
       <c r="Q2" t="n">
-        <v>242790000</v>
-      </c>
-      <c r="R2" t="inlineStr"/>
+        <v>200955000</v>
+      </c>
+      <c r="R2" t="n">
+        <v>596000</v>
+      </c>
       <c r="S2" t="n">
-        <v>-79872000</v>
+        <v>19823000</v>
       </c>
       <c r="T2" t="n">
-        <v>525025000</v>
+        <v>390550689</v>
       </c>
       <c r="U2" t="n">
-        <v>525025000</v>
+        <v>390270986</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.144</v>
+        <v>0.035</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.144</v>
+        <v>0.035</v>
       </c>
       <c r="X2" t="n">
-        <v>-75793000</v>
+        <v>13491000</v>
       </c>
       <c r="Y2" t="n">
-        <v>-75793000</v>
+        <v>13491000</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>-75793000</v>
+        <v>13491000</v>
       </c>
       <c r="AB2" t="n">
-        <v>-75793000</v>
+        <v>13491000</v>
       </c>
       <c r="AC2" t="n">
-        <v>-75793000</v>
+        <v>13491000</v>
       </c>
       <c r="AD2" t="n">
-        <v>-6103000</v>
+        <v>5555000</v>
       </c>
       <c r="AE2" t="n">
-        <v>-81896000</v>
+        <v>19046000</v>
       </c>
       <c r="AF2" t="n">
-        <v>90000</v>
+        <v>152000</v>
       </c>
       <c r="AG2" t="n">
-        <v>-30049000</v>
-      </c>
-      <c r="AH2" t="inlineStr"/>
+        <v>1532000</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>-1532000</v>
+      </c>
       <c r="AI2" t="n">
-        <v>30049000</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-80000</v>
+        <v>-6920000</v>
       </c>
       <c r="AK2" t="n">
-        <v>4280000</v>
+        <v>6190000</v>
       </c>
       <c r="AL2" t="n">
-        <v>2024000</v>
+        <v>777000</v>
       </c>
       <c r="AM2" t="n">
-        <v>6224000</v>
+        <v>47000</v>
       </c>
       <c r="AN2" t="n">
-        <v>-51857000</v>
+        <v>24282000</v>
       </c>
       <c r="AO2" t="n">
-        <v>205464000</v>
+        <v>162463000</v>
       </c>
       <c r="AP2" t="n">
-        <v>2911000</v>
+        <v>2514000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>37383000</v>
+        <v>22093000</v>
       </c>
       <c r="AR2" t="n">
-        <v>37383000</v>
+        <v>22093000</v>
       </c>
       <c r="AS2" t="n">
-        <v>12900000</v>
+        <v>6033000</v>
       </c>
       <c r="AT2" t="n">
-        <v>91304000</v>
+        <v>89800000</v>
       </c>
       <c r="AU2" t="n">
-        <v>91304000</v>
-      </c>
-      <c r="AV2" t="inlineStr"/>
+        <v>89800000</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>596000</v>
+      </c>
       <c r="AW2" t="n">
-        <v>153607000</v>
+        <v>186745000</v>
       </c>
       <c r="AX2" t="n">
-        <v>37326000</v>
+        <v>38492000</v>
       </c>
       <c r="AY2" t="n">
-        <v>190933000</v>
+        <v>225237000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>190933000</v>
+        <v>225237000</v>
       </c>
     </row>
     <row r="3">
@@ -990,160 +996,154 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44651</v>
+        <v>45382</v>
       </c>
       <c r="B4" t="n">
-        <v>447344</v>
+        <v>-2239291.870177</v>
       </c>
       <c r="C4" t="n">
-        <v>0.292</v>
+        <v>0.074521</v>
       </c>
       <c r="D4" t="n">
-        <v>40384000</v>
+        <v>-12440000</v>
       </c>
       <c r="E4" t="n">
-        <v>1532000</v>
+        <v>-30049000</v>
       </c>
       <c r="F4" t="n">
-        <v>1532000</v>
+        <v>-30049000</v>
       </c>
       <c r="G4" t="n">
-        <v>13491000</v>
+        <v>-75793000</v>
       </c>
       <c r="H4" t="n">
-        <v>22093000</v>
+        <v>37383000</v>
       </c>
       <c r="I4" t="n">
-        <v>38492000</v>
+        <v>37326000</v>
       </c>
       <c r="J4" t="n">
-        <v>41916000</v>
+        <v>-42489000</v>
       </c>
       <c r="K4" t="n">
-        <v>19823000</v>
+        <v>-79872000</v>
       </c>
       <c r="L4" t="n">
-        <v>-6920000</v>
+        <v>-80000</v>
       </c>
       <c r="M4" t="n">
-        <v>777000</v>
+        <v>2024000</v>
       </c>
       <c r="N4" t="n">
-        <v>47000</v>
+        <v>6224000</v>
       </c>
       <c r="O4" t="n">
-        <v>12406344</v>
+        <v>-47983291.870177</v>
       </c>
       <c r="P4" t="n">
-        <v>13491000</v>
+        <v>-75793000</v>
       </c>
       <c r="Q4" t="n">
-        <v>200955000</v>
-      </c>
-      <c r="R4" t="n">
-        <v>596000</v>
-      </c>
+        <v>242790000</v>
+      </c>
+      <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>19823000</v>
+        <v>-79872000</v>
       </c>
       <c r="T4" t="n">
-        <v>390550689</v>
+        <v>525025000</v>
       </c>
       <c r="U4" t="n">
-        <v>390270986</v>
+        <v>525025000</v>
       </c>
       <c r="V4" t="n">
-        <v>0.035</v>
+        <v>-0.144</v>
       </c>
       <c r="W4" t="n">
-        <v>0.035</v>
+        <v>-0.144</v>
       </c>
       <c r="X4" t="n">
-        <v>13491000</v>
+        <v>-75793000</v>
       </c>
       <c r="Y4" t="n">
-        <v>13491000</v>
+        <v>-75793000</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>13491000</v>
+        <v>-75793000</v>
       </c>
       <c r="AB4" t="n">
-        <v>13491000</v>
+        <v>-75793000</v>
       </c>
       <c r="AC4" t="n">
-        <v>13491000</v>
+        <v>-75793000</v>
       </c>
       <c r="AD4" t="n">
-        <v>5555000</v>
+        <v>-6103000</v>
       </c>
       <c r="AE4" t="n">
-        <v>19046000</v>
+        <v>-81896000</v>
       </c>
       <c r="AF4" t="n">
-        <v>152000</v>
+        <v>90000</v>
       </c>
       <c r="AG4" t="n">
-        <v>1532000</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>-1532000</v>
-      </c>
+        <v>-30049000</v>
+      </c>
+      <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>30049000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-6920000</v>
+        <v>-80000</v>
       </c>
       <c r="AK4" t="n">
-        <v>6190000</v>
+        <v>4280000</v>
       </c>
       <c r="AL4" t="n">
-        <v>777000</v>
+        <v>2024000</v>
       </c>
       <c r="AM4" t="n">
-        <v>47000</v>
+        <v>6224000</v>
       </c>
       <c r="AN4" t="n">
-        <v>24282000</v>
+        <v>-51857000</v>
       </c>
       <c r="AO4" t="n">
-        <v>162463000</v>
+        <v>205464000</v>
       </c>
       <c r="AP4" t="n">
-        <v>2514000</v>
+        <v>2911000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>22093000</v>
+        <v>37383000</v>
       </c>
       <c r="AR4" t="n">
-        <v>22093000</v>
+        <v>37383000</v>
       </c>
       <c r="AS4" t="n">
-        <v>6033000</v>
+        <v>12900000</v>
       </c>
       <c r="AT4" t="n">
-        <v>89800000</v>
+        <v>91304000</v>
       </c>
       <c r="AU4" t="n">
-        <v>89800000</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>596000</v>
-      </c>
+        <v>91304000</v>
+      </c>
+      <c r="AV4" t="inlineStr"/>
       <c r="AW4" t="n">
-        <v>186745000</v>
+        <v>153607000</v>
       </c>
       <c r="AX4" t="n">
-        <v>38492000</v>
+        <v>37326000</v>
       </c>
       <c r="AY4" t="n">
-        <v>225237000</v>
+        <v>190933000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>225237000</v>
+        <v>190933000</v>
       </c>
     </row>
   </sheetData>
@@ -1434,163 +1434,163 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45382</v>
+        <v>44651</v>
       </c>
       <c r="B2" t="n">
-        <v>528125000</v>
+        <v>509717500</v>
       </c>
       <c r="C2" t="n">
-        <v>528125000</v>
+        <v>509717500</v>
       </c>
       <c r="D2" t="n">
-        <v>25410000</v>
+        <v>20175000</v>
       </c>
       <c r="E2" t="n">
-        <v>189522000</v>
+        <v>255451000</v>
       </c>
       <c r="F2" t="n">
-        <v>189522000</v>
+        <v>255451000</v>
       </c>
       <c r="G2" t="n">
-        <v>130875000</v>
+        <v>225396000</v>
       </c>
       <c r="H2" t="n">
-        <v>189522000</v>
+        <v>255451000</v>
       </c>
       <c r="I2" t="n">
-        <v>25410000</v>
+        <v>20175000</v>
       </c>
       <c r="J2" t="n">
-        <v>189522000</v>
+        <v>255451000</v>
       </c>
       <c r="K2" t="n">
-        <v>189522000</v>
+        <v>255451000</v>
       </c>
       <c r="L2" t="n">
-        <v>189522000</v>
+        <v>255451000</v>
       </c>
       <c r="M2" t="n">
-        <v>189522000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>-3468000</v>
-      </c>
+        <v>255451000</v>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="n">
-        <v>306388000</v>
+        <v>292898000</v>
       </c>
       <c r="P2" t="n">
-        <v>5281000</v>
+        <v>5097000</v>
       </c>
       <c r="Q2" t="n">
-        <v>5281000</v>
+        <v>5097000</v>
       </c>
       <c r="R2" t="n">
-        <v>46641000</v>
+        <v>34693000</v>
       </c>
       <c r="S2" t="n">
-        <v>8308000</v>
-      </c>
-      <c r="T2" t="inlineStr"/>
+        <v>10497000</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
       <c r="U2" t="n">
-        <v>6233000</v>
+        <v>9247000</v>
       </c>
       <c r="V2" t="n">
-        <v>6233000</v>
+        <v>9247000</v>
       </c>
       <c r="W2" t="n">
-        <v>2075000</v>
+        <v>1250000</v>
       </c>
       <c r="X2" t="n">
-        <v>38333000</v>
+        <v>24196000</v>
       </c>
       <c r="Y2" t="n">
-        <v>19177000</v>
+        <v>10928000</v>
       </c>
       <c r="Z2" t="n">
-        <v>19177000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>2300000</v>
-      </c>
+        <v>10928000</v>
+      </c>
+      <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="n">
-        <v>12744000</v>
+        <v>9458000</v>
       </c>
       <c r="AC2" t="n">
-        <v>7977000</v>
-      </c>
-      <c r="AD2" t="inlineStr"/>
+        <v>3581000</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
       <c r="AE2" t="n">
-        <v>4767000</v>
+        <v>5877000</v>
       </c>
       <c r="AF2" t="n">
-        <v>236163000</v>
+        <v>290144000</v>
       </c>
       <c r="AG2" t="n">
-        <v>66955000</v>
+        <v>40552000</v>
       </c>
       <c r="AH2" t="n">
-        <v>7892000</v>
+        <v>2144000</v>
       </c>
       <c r="AI2" t="n">
-        <v>6434000</v>
+        <v>594000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>52629000</v>
+        <v>37814000</v>
       </c>
       <c r="AK2" t="n">
-        <v>-89665000</v>
+        <v>-46103000</v>
       </c>
       <c r="AL2" t="n">
-        <v>142294000</v>
+        <v>83917000</v>
       </c>
       <c r="AM2" t="n">
-        <v>128000</v>
-      </c>
-      <c r="AN2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>223000</v>
+      </c>
       <c r="AO2" t="n">
-        <v>73167000</v>
+        <v>42208000</v>
       </c>
       <c r="AP2" t="n">
-        <v>68999000</v>
+        <v>41486000</v>
       </c>
       <c r="AQ2" t="n">
         <v>0</v>
       </c>
       <c r="AR2" t="n">
-        <v>169208000</v>
+        <v>249592000</v>
       </c>
       <c r="AS2" t="n">
-        <v>3938000</v>
+        <v>2566000</v>
       </c>
       <c r="AT2" t="n">
-        <v>3576000</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>137000</v>
-      </c>
+        <v>3746000</v>
+      </c>
+      <c r="AU2" t="inlineStr"/>
       <c r="AV2" t="n">
-        <v>3439000</v>
+        <v>3746000</v>
       </c>
       <c r="AW2" t="n">
-        <v>16211000</v>
+        <v>63000</v>
       </c>
       <c r="AX2" t="n">
-        <v>1405000</v>
+        <v>842000</v>
       </c>
       <c r="AY2" t="n">
-        <v>2647000</v>
+        <v>1105000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>141431000</v>
+        <v>241270000</v>
       </c>
       <c r="BA2" t="n">
-        <v>141431000</v>
+        <v>241270000</v>
       </c>
       <c r="BB2" t="n">
-        <v>98000000</v>
+        <v>0</v>
       </c>
       <c r="BC2" t="n">
-        <v>43431000</v>
+        <v>241270000</v>
       </c>
     </row>
     <row r="3">
@@ -1756,163 +1756,163 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44651</v>
+        <v>45382</v>
       </c>
       <c r="B4" t="n">
-        <v>509717500</v>
+        <v>528125000</v>
       </c>
       <c r="C4" t="n">
-        <v>509717500</v>
+        <v>528125000</v>
       </c>
       <c r="D4" t="n">
-        <v>20175000</v>
+        <v>25410000</v>
       </c>
       <c r="E4" t="n">
-        <v>255451000</v>
+        <v>189522000</v>
       </c>
       <c r="F4" t="n">
-        <v>255451000</v>
+        <v>189522000</v>
       </c>
       <c r="G4" t="n">
-        <v>225396000</v>
+        <v>130875000</v>
       </c>
       <c r="H4" t="n">
-        <v>255451000</v>
+        <v>189522000</v>
       </c>
       <c r="I4" t="n">
-        <v>20175000</v>
+        <v>25410000</v>
       </c>
       <c r="J4" t="n">
-        <v>255451000</v>
+        <v>189522000</v>
       </c>
       <c r="K4" t="n">
-        <v>255451000</v>
+        <v>189522000</v>
       </c>
       <c r="L4" t="n">
-        <v>255451000</v>
+        <v>189522000</v>
       </c>
       <c r="M4" t="n">
-        <v>255451000</v>
-      </c>
-      <c r="N4" t="inlineStr"/>
+        <v>189522000</v>
+      </c>
+      <c r="N4" t="n">
+        <v>-3468000</v>
+      </c>
       <c r="O4" t="n">
-        <v>292898000</v>
+        <v>306388000</v>
       </c>
       <c r="P4" t="n">
-        <v>5097000</v>
+        <v>5281000</v>
       </c>
       <c r="Q4" t="n">
-        <v>5097000</v>
+        <v>5281000</v>
       </c>
       <c r="R4" t="n">
-        <v>34693000</v>
+        <v>46641000</v>
       </c>
       <c r="S4" t="n">
-        <v>10497000</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
+        <v>8308000</v>
+      </c>
+      <c r="T4" t="inlineStr"/>
       <c r="U4" t="n">
-        <v>9247000</v>
+        <v>6233000</v>
       </c>
       <c r="V4" t="n">
-        <v>9247000</v>
+        <v>6233000</v>
       </c>
       <c r="W4" t="n">
-        <v>1250000</v>
+        <v>2075000</v>
       </c>
       <c r="X4" t="n">
-        <v>24196000</v>
+        <v>38333000</v>
       </c>
       <c r="Y4" t="n">
-        <v>10928000</v>
+        <v>19177000</v>
       </c>
       <c r="Z4" t="n">
-        <v>10928000</v>
-      </c>
-      <c r="AA4" t="inlineStr"/>
+        <v>19177000</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2300000</v>
+      </c>
       <c r="AB4" t="n">
-        <v>9458000</v>
+        <v>12744000</v>
       </c>
       <c r="AC4" t="n">
-        <v>3581000</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
+        <v>7977000</v>
+      </c>
+      <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="n">
-        <v>5877000</v>
+        <v>4767000</v>
       </c>
       <c r="AF4" t="n">
-        <v>290144000</v>
+        <v>236163000</v>
       </c>
       <c r="AG4" t="n">
-        <v>40552000</v>
+        <v>66955000</v>
       </c>
       <c r="AH4" t="n">
-        <v>2144000</v>
+        <v>7892000</v>
       </c>
       <c r="AI4" t="n">
-        <v>594000</v>
+        <v>6434000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>37814000</v>
+        <v>52629000</v>
       </c>
       <c r="AK4" t="n">
-        <v>-46103000</v>
+        <v>-89665000</v>
       </c>
       <c r="AL4" t="n">
-        <v>83917000</v>
+        <v>142294000</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>223000</v>
-      </c>
+        <v>128000</v>
+      </c>
+      <c r="AN4" t="inlineStr"/>
       <c r="AO4" t="n">
-        <v>42208000</v>
+        <v>73167000</v>
       </c>
       <c r="AP4" t="n">
-        <v>41486000</v>
+        <v>68999000</v>
       </c>
       <c r="AQ4" t="n">
         <v>0</v>
       </c>
       <c r="AR4" t="n">
-        <v>249592000</v>
+        <v>169208000</v>
       </c>
       <c r="AS4" t="n">
-        <v>2566000</v>
+        <v>3938000</v>
       </c>
       <c r="AT4" t="n">
-        <v>3746000</v>
-      </c>
-      <c r="AU4" t="inlineStr"/>
+        <v>3576000</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>137000</v>
+      </c>
       <c r="AV4" t="n">
-        <v>3746000</v>
+        <v>3439000</v>
       </c>
       <c r="AW4" t="n">
-        <v>63000</v>
+        <v>16211000</v>
       </c>
       <c r="AX4" t="n">
-        <v>842000</v>
+        <v>1405000</v>
       </c>
       <c r="AY4" t="n">
-        <v>1105000</v>
+        <v>2647000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>241270000</v>
+        <v>141431000</v>
       </c>
       <c r="BA4" t="n">
-        <v>241270000</v>
+        <v>141431000</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>98000000</v>
       </c>
       <c r="BC4" t="n">
-        <v>241270000</v>
+        <v>43431000</v>
       </c>
     </row>
   </sheetData>
@@ -2118,102 +2118,114 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45382</v>
+        <v>44651</v>
       </c>
       <c r="B2" t="n">
-        <v>-48392000</v>
-      </c>
-      <c r="C2" t="inlineStr"/>
+        <v>27345000</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>205539000</v>
       </c>
       <c r="E2" t="n">
-        <v>-32813000</v>
+        <v>-205000</v>
       </c>
       <c r="F2" t="n">
-        <v>91431000</v>
+        <v>241270000</v>
       </c>
       <c r="G2" t="n">
-        <v>104496000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1000</v>
-      </c>
+        <v>64862000</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
-        <v>-13066000</v>
+        <v>176408000</v>
       </c>
       <c r="J2" t="n">
-        <v>-24095000</v>
+        <v>149016000</v>
       </c>
       <c r="K2" t="n">
-        <v>-2024000</v>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+        <v>-777000</v>
+      </c>
+      <c r="L2" t="n">
+        <v>-26000000</v>
+      </c>
+      <c r="M2" t="n">
+        <v>-26000000</v>
+      </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>205539000</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
+        <v>205539000</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
       <c r="S2" t="n">
-        <v>26608000</v>
+        <v>-158000</v>
       </c>
       <c r="T2" t="n">
-        <v>6421000</v>
+        <v>47000</v>
       </c>
       <c r="U2" t="n">
-        <v>53000000</v>
-      </c>
-      <c r="V2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
       <c r="W2" t="n">
-        <v>-32813000</v>
+        <v>-205000</v>
       </c>
       <c r="X2" t="n">
-        <v>-32813000</v>
+        <v>-205000</v>
       </c>
       <c r="Y2" t="n">
-        <v>-15579000</v>
+        <v>27550000</v>
       </c>
       <c r="Z2" t="n">
-        <v>-351000</v>
-      </c>
-      <c r="AA2" t="inlineStr"/>
+        <v>-10528000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0</v>
+      </c>
       <c r="AB2" t="n">
-        <v>-2594000</v>
+        <v>-2259000</v>
       </c>
       <c r="AC2" t="n">
-        <v>-1424000</v>
+        <v>-4110000</v>
       </c>
       <c r="AD2" t="n">
-        <v>-2399000</v>
+        <v>-2533000</v>
       </c>
       <c r="AE2" t="n">
-        <v>1810000</v>
+        <v>2488000</v>
       </c>
       <c r="AF2" t="n">
-        <v>106000</v>
+        <v>454000</v>
       </c>
       <c r="AG2" t="n">
-        <v>-687000</v>
+        <v>1442000</v>
       </c>
       <c r="AH2" t="n">
-        <v>-4200000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>6030000</v>
-      </c>
+        <v>-802000</v>
+      </c>
+      <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="n">
-        <v>37383000</v>
+        <v>22093000</v>
       </c>
       <c r="AK2" t="n">
-        <v>37383000</v>
+        <v>22093000</v>
       </c>
       <c r="AL2" t="n">
-        <v>-81896000</v>
+        <v>19046000</v>
       </c>
     </row>
     <row r="3">
@@ -2322,114 +2334,102 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44651</v>
+        <v>45382</v>
       </c>
       <c r="B4" t="n">
-        <v>27345000</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
+        <v>-48392000</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>205539000</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-205000</v>
+        <v>-32813000</v>
       </c>
       <c r="F4" t="n">
-        <v>241270000</v>
+        <v>91431000</v>
       </c>
       <c r="G4" t="n">
-        <v>64862000</v>
-      </c>
-      <c r="H4" t="inlineStr"/>
+        <v>104496000</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1000</v>
+      </c>
       <c r="I4" t="n">
-        <v>176408000</v>
+        <v>-13066000</v>
       </c>
       <c r="J4" t="n">
-        <v>149016000</v>
+        <v>-24095000</v>
       </c>
       <c r="K4" t="n">
-        <v>-777000</v>
-      </c>
-      <c r="L4" t="n">
-        <v>-26000000</v>
-      </c>
-      <c r="M4" t="n">
-        <v>-26000000</v>
-      </c>
+        <v>-2024000</v>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
-        <v>205539000</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>205539000</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>-158000</v>
+        <v>26608000</v>
       </c>
       <c r="T4" t="n">
-        <v>47000</v>
+        <v>6421000</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0</v>
-      </c>
+        <v>53000000</v>
+      </c>
+      <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>-205000</v>
+        <v>-32813000</v>
       </c>
       <c r="X4" t="n">
-        <v>-205000</v>
+        <v>-32813000</v>
       </c>
       <c r="Y4" t="n">
-        <v>27550000</v>
+        <v>-15579000</v>
       </c>
       <c r="Z4" t="n">
-        <v>-10528000</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0</v>
-      </c>
+        <v>-351000</v>
+      </c>
+      <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="n">
-        <v>-2259000</v>
+        <v>-2594000</v>
       </c>
       <c r="AC4" t="n">
-        <v>-4110000</v>
+        <v>-1424000</v>
       </c>
       <c r="AD4" t="n">
-        <v>-2533000</v>
+        <v>-2399000</v>
       </c>
       <c r="AE4" t="n">
-        <v>2488000</v>
+        <v>1810000</v>
       </c>
       <c r="AF4" t="n">
-        <v>454000</v>
+        <v>106000</v>
       </c>
       <c r="AG4" t="n">
-        <v>1442000</v>
+        <v>-687000</v>
       </c>
       <c r="AH4" t="n">
-        <v>-802000</v>
-      </c>
-      <c r="AI4" t="inlineStr"/>
+        <v>-4200000</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>6030000</v>
+      </c>
       <c r="AJ4" t="n">
-        <v>22093000</v>
+        <v>37383000</v>
       </c>
       <c r="AK4" t="n">
-        <v>22093000</v>
+        <v>37383000</v>
       </c>
       <c r="AL4" t="n">
-        <v>19046000</v>
+        <v>-81896000</v>
       </c>
     </row>
   </sheetData>
@@ -2934,172 +2934,172 @@
       </c>
       <c r="CT1" t="inlineStr">
         <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="CU1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="CV1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="CW1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="CX1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="CY1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="CZ1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DA1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
           <t>hasPrePostMarketData</t>
         </is>
       </c>
-      <c r="CU1" t="inlineStr">
+      <c r="DI1" t="inlineStr">
         <is>
           <t>firstTradeDateMilliseconds</t>
         </is>
       </c>
-      <c r="CV1" t="inlineStr">
+      <c r="DJ1" t="inlineStr">
         <is>
           <t>regularMarketChange</t>
         </is>
       </c>
-      <c r="CW1" t="inlineStr">
+      <c r="DK1" t="inlineStr">
         <is>
           <t>regularMarketDayRange</t>
         </is>
       </c>
-      <c r="CX1" t="inlineStr">
+      <c r="DL1" t="inlineStr">
         <is>
           <t>fullExchangeName</t>
         </is>
       </c>
-      <c r="CY1" t="inlineStr">
+      <c r="DM1" t="inlineStr">
         <is>
           <t>averageDailyVolume3Month</t>
         </is>
       </c>
-      <c r="CZ1" t="inlineStr">
+      <c r="DN1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChange</t>
         </is>
       </c>
-      <c r="DA1" t="inlineStr">
+      <c r="DO1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChangePercent</t>
         </is>
       </c>
-      <c r="DB1" t="inlineStr">
+      <c r="DP1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekRange</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
+      <c r="DQ1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChange</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
+      <c r="DR1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChangePercent</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
+      <c r="DS1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekChangePercent</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
+      <c r="DT1" t="inlineStr">
         <is>
           <t>epsTrailingTwelveMonths</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
+      <c r="DU1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChange</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
+      <c r="DV1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="DI1" t="inlineStr">
+      <c r="DW1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChange</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
         <is>
           <t>sourceInterval</t>
         </is>
       </c>
-      <c r="DL1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>exchangeDataDelayedBy</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>longName</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
         </is>
       </c>
       <c r="EB1" t="inlineStr">
@@ -3229,7 +3229,7 @@
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="AE2" t="n">
         <v>75000</v>
@@ -3345,7 +3345,7 @@
         <v>0</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.27294624</v>
+        <v>0.24487448</v>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
@@ -3452,131 +3452,131 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="CT2" t="b">
-        <v>0</v>
+      <c r="CT2" t="inlineStr">
+        <is>
+          <t>PRE</t>
+        </is>
       </c>
       <c r="CU2" t="n">
+        <v>5.9701433</v>
+      </c>
+      <c r="CV2" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="CW2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="CX2" t="n">
+        <v>1744595437</v>
+      </c>
+      <c r="CY2" t="inlineStr">
+        <is>
+          <t>HKG</t>
+        </is>
+      </c>
+      <c r="CZ2" t="inlineStr">
+        <is>
+          <t>finmb_1765408422</t>
+        </is>
+      </c>
+      <c r="DA2" t="inlineStr">
+        <is>
+          <t>Asia/Hong_Kong</t>
+        </is>
+      </c>
+      <c r="DB2" t="inlineStr">
+        <is>
+          <t>HKT</t>
+        </is>
+      </c>
+      <c r="DC2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="DD2" t="inlineStr">
+        <is>
+          <t>hk_market</t>
+        </is>
+      </c>
+      <c r="DE2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DF2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DG2" t="inlineStr">
+        <is>
+          <t>CLARITY MEDICAL</t>
+        </is>
+      </c>
+      <c r="DH2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DI2" t="n">
         <v>1645147800000</v>
       </c>
-      <c r="CV2" t="n">
+      <c r="DJ2" t="n">
         <v>0.01999998</v>
       </c>
-      <c r="CW2" t="inlineStr">
+      <c r="DK2" t="inlineStr">
         <is>
           <t>0.355 - 0.36</t>
         </is>
       </c>
-      <c r="CX2" t="inlineStr">
+      <c r="DL2" t="inlineStr">
         <is>
           <t>HKSE</t>
         </is>
       </c>
-      <c r="CY2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CZ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DB2" t="inlineStr">
+      <c r="DM2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP2" t="inlineStr">
         <is>
           <t>0.355 - 0.36</t>
         </is>
       </c>
-      <c r="DC2" t="n">
+      <c r="DQ2" t="n">
         <v>-0.005000025</v>
       </c>
-      <c r="DD2" t="n">
+      <c r="DR2" t="n">
         <v>-0.013888958</v>
       </c>
-      <c r="DE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DF2" t="n">
+      <c r="DS2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT2" t="n">
         <v>-0.14</v>
       </c>
-      <c r="DG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DI2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DK2" t="n">
+      <c r="DU2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY2" t="n">
         <v>15</v>
       </c>
-      <c r="DL2" t="n">
+      <c r="DZ2" t="n">
         <v>15</v>
       </c>
-      <c r="DM2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DN2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="DO2" t="n">
-        <v>1744595437</v>
-      </c>
-      <c r="DP2" t="inlineStr">
-        <is>
-          <t>HKG</t>
-        </is>
-      </c>
-      <c r="DQ2" t="inlineStr">
-        <is>
-          <t>finmb_1765408422</t>
-        </is>
-      </c>
-      <c r="DR2" t="inlineStr">
-        <is>
-          <t>Asia/Hong_Kong</t>
-        </is>
-      </c>
-      <c r="DS2" t="inlineStr">
-        <is>
-          <t>HKT</t>
-        </is>
-      </c>
-      <c r="DT2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="DU2" t="inlineStr">
-        <is>
-          <t>hk_market</t>
-        </is>
-      </c>
-      <c r="DV2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DW2" t="inlineStr">
-        <is>
-          <t>CLARITY MEDICAL</t>
-        </is>
-      </c>
-      <c r="DX2" t="inlineStr">
+      <c r="EA2" t="inlineStr">
         <is>
           <t>Clarity Medical Group Holding Limited</t>
         </is>
-      </c>
-      <c r="DY2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="DZ2" t="n">
-        <v>5.9701433</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>0.355</v>
       </c>
       <c r="EB2" t="inlineStr"/>
     </row>
